--- a/y11581/samples/handover_records.xlsx
+++ b/y11581/samples/handover_records.xlsx
@@ -79,10 +79,10 @@
     <t>经理张</t>
   </si>
   <si>
+    <t>经理孙</t>
+  </si>
+  <si>
     <t>经理赵</t>
-  </si>
-  <si>
-    <t>经理钱</t>
   </si>
   <si>
     <t>经理周</t>
@@ -489,13 +489,13 @@
         <v>21</v>
       </c>
       <c r="F2">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="G2">
-        <v>122976</v>
+        <v>143429</v>
       </c>
       <c r="H2">
-        <v>5815</v>
+        <v>16121</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -515,13 +515,13 @@
         <v>22</v>
       </c>
       <c r="F3">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="G3">
-        <v>105754</v>
+        <v>195769</v>
       </c>
       <c r="H3">
-        <v>14624</v>
+        <v>10882</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -535,19 +535,19 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="G4">
-        <v>103813</v>
+        <v>191934</v>
       </c>
       <c r="H4">
-        <v>7031</v>
+        <v>12915</v>
       </c>
     </row>
     <row r="5" spans="1:8">
